--- a/processo_2/synthetic_proposals/PROPOSTA_014/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_014/ficha_pontuacao.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Quantidade Declarada</t>
+          <t>Qtde</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>1.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,29 +804,21 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>9485-4984</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 2</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -966,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -989,7 +981,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1058,7 +1050,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1083,7 +1075,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,7 +1118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1149,7 +1141,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1176,13 +1168,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
@@ -1195,7 +1187,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1218,7 +1210,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1241,17 +1233,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
@@ -1264,17 +1256,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1287,7 +1279,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1310,7 +1302,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1333,7 +1325,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1423,13 +1415,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1551,7 +1543,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,7 +1566,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1620,7 +1612,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1643,7 +1635,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1660,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1807,13 +1799,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
@@ -1830,13 +1822,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -1851,7 +1843,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1866,7 +1858,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
